--- a/backend/static/sample_upload.xlsx
+++ b/backend/static/sample_upload.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>Courier</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Platform Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -441,12 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>195043000000001</t>
+          <t>195042600200336</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Delhivery</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
@@ -458,12 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>195043000000002</t>
+          <t>195042600200337</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Xpressbees</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Transit</t>
         </is>
       </c>
     </row>
@@ -475,12 +490,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>195043000000003</t>
+          <t>987654321</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shadowfax</t>
+          <t>Blue Dart</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INV-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>554433221</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DTDC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
